--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_coquimbo.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_coquimbo.xlsx
@@ -404,7 +404,7 @@
         <v>26.65841908939249</v>
       </c>
       <c r="D2">
-        <v>1.74166693872221</v>
+        <v>3.25120360777622</v>
       </c>
       <c r="E2">
         <v>19.53917599428435</v>
@@ -429,7 +429,7 @@
         <v>28.06063008203317</v>
       </c>
       <c r="D3">
-        <v>1.686685236768802</v>
+        <v>3.202330814054116</v>
       </c>
       <c r="E3">
         <v>19.60428738929962</v>
@@ -454,7 +454,7 @@
         <v>28.33375666751333</v>
       </c>
       <c r="D4">
-        <v>1.47177570093458</v>
+        <v>2.524527092016672</v>
       </c>
       <c r="E4">
         <v>23.58590441621294</v>
@@ -479,7 +479,7 @@
         <v>36.4186543253827</v>
       </c>
       <c r="D5">
-        <v>1.353082851637765</v>
+        <v>2.667616334283001</v>
       </c>
       <c r="E5">
         <v>21.55578300921187</v>
@@ -504,7 +504,7 @@
         <v>26.99849170437406</v>
       </c>
       <c r="D6">
-        <v>1.474644128113879</v>
+        <v>2.450110864745011</v>
       </c>
       <c r="E6">
         <v>24.32140931152255</v>
@@ -529,7 +529,7 @@
         <v>26.1497963643588</v>
       </c>
       <c r="D7">
-        <v>1.604942208051017</v>
+        <v>2.765659340659341</v>
       </c>
       <c r="E7">
         <v>22.27730346705836</v>
@@ -554,7 +554,7 @@
         <v>27.22577009767092</v>
       </c>
       <c r="D8">
-        <v>1.507788161993769</v>
+        <v>2.557770838337737</v>
       </c>
       <c r="E8">
         <v>23.50649350649351</v>
@@ -579,7 +579,7 @@
         <v>23.97293378443693</v>
       </c>
       <c r="D9">
-        <v>1.327700534759358</v>
+        <v>1.947599623470348</v>
       </c>
       <c r="E9">
         <v>29.28689579121485</v>
@@ -604,7 +604,7 @@
         <v>28.09241336247268</v>
       </c>
       <c r="D10">
-        <v>1.506443420186248</v>
+        <v>2.611709067188519</v>
       </c>
       <c r="E10">
         <v>23.01283494708399</v>
@@ -629,7 +629,7 @@
         <v>26.3904831472399</v>
       </c>
       <c r="D11">
-        <v>1.613843044796228</v>
+        <v>2.811088295687885</v>
       </c>
       <c r="E11">
         <v>21.9637909928484</v>
@@ -654,7 +654,7 @@
         <v>28.06377282595666</v>
       </c>
       <c r="D12">
-        <v>1.600285616847131</v>
+        <v>2.904859552735433</v>
       </c>
       <c r="E12">
         <v>21.18611418500759</v>
@@ -679,7 +679,7 @@
         <v>21.83609958506224</v>
       </c>
       <c r="D13">
-        <v>1.462378640776699</v>
+        <v>2.148428794294629</v>
       </c>
       <c r="E13">
         <v>27.64292755051749</v>
@@ -704,7 +704,7 @@
         <v>27.62125622933833</v>
       </c>
       <c r="D14">
-        <v>1.540982360097324</v>
+        <v>2.682949430765158</v>
       </c>
       <c r="E14">
         <v>22.60390795655166</v>
@@ -729,7 +729,7 @@
         <v>26.51779483600837</v>
       </c>
       <c r="D15">
-        <v>1.502358902673423</v>
+        <v>2.497240778390938</v>
       </c>
       <c r="E15">
         <v>24.04161720550242</v>
@@ -754,7 +754,7 @@
         <v>21.33905013192612</v>
       </c>
       <c r="D16">
-        <v>1.355992844364937</v>
+        <v>1.908118313404657</v>
       </c>
       <c r="E16">
         <v>30.16324981017464</v>

--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_coquimbo.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_coquimbo.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.65841908939249</v>
+      </c>
+      <c r="C2">
         <v>30.75783988453392</v>
-      </c>
-      <c r="C2">
-        <v>26.65841908939249</v>
       </c>
       <c r="D2">
         <v>3.25120360777622</v>
       </c>
       <c r="E2">
-        <v>19.53917599428435</v>
+        <v>16.93498452012384</v>
       </c>
       <c r="F2">
         <v>63.52583948559181</v>
       </c>
       <c r="G2">
-        <v>16.93498452012384</v>
+        <v>19.53917599428435</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.06063008203317</v>
+      </c>
+      <c r="C3">
         <v>31.22725471120239</v>
-      </c>
-      <c r="C3">
-        <v>28.06063008203317</v>
       </c>
       <c r="D3">
         <v>3.202330814054116</v>
       </c>
       <c r="E3">
+        <v>17.61629901637366</v>
+      </c>
+      <c r="F3">
+        <v>62.77941359432671</v>
+      </c>
+      <c r="G3">
         <v>19.60428738929962</v>
-      </c>
-      <c r="F3">
-        <v>62.77941359432672</v>
-      </c>
-      <c r="G3">
-        <v>17.61629901637367</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>28.33375666751333</v>
+      </c>
+      <c r="C4">
         <v>39.61137922275844</v>
-      </c>
-      <c r="C4">
-        <v>28.33375666751333</v>
       </c>
       <c r="D4">
         <v>2.524527092016672</v>
       </c>
       <c r="E4">
-        <v>23.58590441621294</v>
+        <v>16.8708408953418</v>
       </c>
       <c r="F4">
         <v>59.54325468844525</v>
       </c>
       <c r="G4">
-        <v>16.8708408953418</v>
+        <v>23.58590441621294</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>36.4186543253827</v>
+      </c>
+      <c r="C5">
         <v>37.48665005339979</v>
-      </c>
-      <c r="C5">
-        <v>36.4186543253827</v>
       </c>
       <c r="D5">
         <v>2.667616334283001</v>
       </c>
       <c r="E5">
-        <v>21.55578300921187</v>
+        <v>20.94165813715455</v>
       </c>
       <c r="F5">
         <v>57.50255885363357</v>
       </c>
       <c r="G5">
-        <v>20.94165813715455</v>
+        <v>21.55578300921187</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>26.99849170437406</v>
+      </c>
+      <c r="C6">
         <v>40.81447963800905</v>
-      </c>
-      <c r="C6">
-        <v>26.99849170437406</v>
       </c>
       <c r="D6">
         <v>2.450110864745011</v>
       </c>
       <c r="E6">
-        <v>24.32140931152255</v>
+        <v>16.08844148840554</v>
       </c>
       <c r="F6">
-        <v>59.5901492000719</v>
+        <v>59.59014920007191</v>
       </c>
       <c r="G6">
-        <v>16.08844148840553</v>
+        <v>24.32140931152256</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>26.1497963643588</v>
+      </c>
+      <c r="C7">
         <v>36.1577431210887</v>
-      </c>
-      <c r="C7">
-        <v>26.1497963643588</v>
       </c>
       <c r="D7">
         <v>2.765659340659341</v>
       </c>
       <c r="E7">
-        <v>22.27730346705836</v>
+        <v>16.11126411456899</v>
       </c>
       <c r="F7">
         <v>61.61143241837267</v>
       </c>
       <c r="G7">
-        <v>16.11126411456899</v>
+        <v>22.27730346705836</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>27.22577009767092</v>
+      </c>
+      <c r="C8">
         <v>39.09654395191586</v>
-      </c>
-      <c r="C8">
-        <v>27.22577009767092</v>
       </c>
       <c r="D8">
         <v>2.557770838337737</v>
       </c>
       <c r="E8">
-        <v>23.50649350649351</v>
+        <v>16.36928289102202</v>
       </c>
       <c r="F8">
         <v>60.12422360248446</v>
       </c>
       <c r="G8">
-        <v>16.36928289102202</v>
+        <v>23.50649350649351</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>23.97293378443693</v>
+      </c>
+      <c r="C9">
         <v>51.34525535685517</v>
-      </c>
-      <c r="C9">
-        <v>23.97293378443693</v>
       </c>
       <c r="D9">
         <v>1.947599623470348</v>
       </c>
       <c r="E9">
-        <v>29.28689579121485</v>
+        <v>13.67395699319978</v>
       </c>
       <c r="F9">
         <v>57.03914721558537</v>
       </c>
       <c r="G9">
-        <v>13.67395699319978</v>
+        <v>29.28689579121485</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.09241336247268</v>
+      </c>
+      <c r="C10">
         <v>38.28910396503279</v>
-      </c>
-      <c r="C10">
-        <v>28.09241336247268</v>
       </c>
       <c r="D10">
         <v>2.611709067188519</v>
       </c>
       <c r="E10">
-        <v>23.01283494708399</v>
+        <v>16.88433535990393</v>
       </c>
       <c r="F10">
         <v>60.10282969301208</v>
       </c>
       <c r="G10">
-        <v>16.88433535990393</v>
+        <v>23.01283494708399</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>26.3904831472399</v>
+      </c>
+      <c r="C11">
         <v>35.57341124908692</v>
-      </c>
-      <c r="C11">
-        <v>26.3904831472399</v>
       </c>
       <c r="D11">
         <v>2.811088295687885</v>
       </c>
       <c r="E11">
-        <v>21.9637909928484</v>
+        <v>16.29405321822048</v>
       </c>
       <c r="F11">
         <v>61.74215578893113</v>
       </c>
       <c r="G11">
-        <v>16.29405321822048</v>
+        <v>21.9637909928484</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>28.06377282595666</v>
+      </c>
+      <c r="C12">
         <v>34.4250722572224</v>
-      </c>
-      <c r="C12">
-        <v>28.06377282595666</v>
       </c>
       <c r="D12">
         <v>2.904859552735433</v>
       </c>
       <c r="E12">
-        <v>21.18611418500759</v>
+        <v>17.27119963932948</v>
       </c>
       <c r="F12">
         <v>61.54268617566294</v>
       </c>
       <c r="G12">
-        <v>17.27119963932948</v>
+        <v>21.18611418500758</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>21.83609958506224</v>
+      </c>
+      <c r="C13">
         <v>46.54564315352697</v>
-      </c>
-      <c r="C13">
-        <v>21.83609958506224</v>
       </c>
       <c r="D13">
         <v>2.148428794294629</v>
       </c>
       <c r="E13">
-        <v>27.64292755051749</v>
+        <v>12.96821094135042</v>
       </c>
       <c r="F13">
         <v>59.38886150813208</v>
       </c>
       <c r="G13">
-        <v>12.96821094135042</v>
+        <v>27.64292755051749</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>27.62125622933833</v>
+      </c>
+      <c r="C14">
         <v>37.27241328267627</v>
-      </c>
-      <c r="C14">
-        <v>27.62125622933833</v>
       </c>
       <c r="D14">
         <v>2.682949430765158</v>
       </c>
       <c r="E14">
-        <v>22.60390795655166</v>
+        <v>16.75095005835004</v>
       </c>
       <c r="F14">
-        <v>60.64514198509829</v>
+        <v>60.64514198509831</v>
       </c>
       <c r="G14">
-        <v>16.75095005835004</v>
+        <v>22.60390795655167</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>26.51779483600837</v>
+      </c>
+      <c r="C15">
         <v>40.04419632472668</v>
-      </c>
-      <c r="C15">
-        <v>26.51779483600837</v>
       </c>
       <c r="D15">
         <v>2.497240778390938</v>
       </c>
       <c r="E15">
-        <v>24.04161720550242</v>
+        <v>15.92067593045178</v>
       </c>
       <c r="F15">
-        <v>60.03770686404582</v>
+        <v>60.0377068640458</v>
       </c>
       <c r="G15">
-        <v>15.92067593045179</v>
+        <v>24.04161720550241</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>21.33905013192612</v>
+      </c>
+      <c r="C16">
         <v>52.40765171503958</v>
-      </c>
-      <c r="C16">
-        <v>21.33905013192612</v>
       </c>
       <c r="D16">
         <v>1.908118313404657</v>
       </c>
       <c r="E16">
-        <v>30.16324981017464</v>
+        <v>12.28170083523159</v>
       </c>
       <c r="F16">
         <v>57.55504935459378</v>
       </c>
       <c r="G16">
-        <v>12.28170083523159</v>
+        <v>30.16324981017464</v>
       </c>
     </row>
   </sheetData>
